--- a/results/link-prediction-gcn/Link/5shot/PROTEINS/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/5shot/PROTEINS/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.4855±0.0000</t>
+          <t>0.4855±0.0002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5161±0.0025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5145±0.0002</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5299±0.0205</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5143±0.0002</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5186±0.0038</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.5142±0.0000</t>
+          <t>0.5145±0.0001</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5257±0.0159</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5257±0.0159</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5257±0.0159</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5150±0.0008</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5339±0.0000</t>
+          <t>0.5354±0.0150</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5188±0.0036</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.4855±0.0000</t>
+          <t>0.4855±0.0002</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.5141±0.0000</t>
+          <t>0.5169±0.0024</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5364±0.0000</t>
+          <t>0.5215±0.0023</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5138±0.0011</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5319±0.0000</t>
+          <t>0.5187±0.0039</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.5155±0.0000</t>
+          <t>0.5179±0.0026</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5167±0.0000</t>
+          <t>0.5149±0.0004</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5143±0.0000</t>
+          <t>0.5149±0.0006</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5143±0.0000</t>
+          <t>0.5149±0.0006</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5143±0.0000</t>
+          <t>0.5149±0.0006</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5366±0.0000</t>
+          <t>0.5155±0.0016</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5145±0.0002</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5158±0.0011</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.4856±0.0000</t>
+          <t>0.4845±0.0018</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5140±0.0000</t>
+          <t>0.5151±0.0002</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5143±0.0000</t>
+          <t>0.5355±0.0017</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5412±0.0091</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5254±0.0000</t>
+          <t>0.5407±0.0183</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5173±0.0000</t>
+          <t>0.5228±0.0049</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5207±0.0039</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5222±0.0000</t>
+          <t>0.5445±0.0097</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5222±0.0000</t>
+          <t>0.5445±0.0097</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5222±0.0000</t>
+          <t>0.5445±0.0097</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5148±0.0000</t>
+          <t>0.5305±0.0044</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5567±0.0000</t>
+          <t>0.5626±0.0016</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5211±0.0000</t>
+          <t>0.5349±0.0121</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.4858±0.0000</t>
+          <t>0.4858±0.0001</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5394±0.0000</t>
+          <t>0.5431±0.0058</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5144±0.0012</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5210±0.0000</t>
+          <t>0.5254±0.0082</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5388±0.0000</t>
+          <t>0.5404±0.0086</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5382±0.0000</t>
+          <t>0.5271±0.0172</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.5484±0.0000</t>
+          <t>0.5221±0.0033</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.5507±0.0000</t>
+          <t>0.5281±0.0035</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.5507±0.0000</t>
+          <t>0.5281±0.0035</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.5507±0.0000</t>
+          <t>0.5281±0.0035</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.5441±0.0000</t>
+          <t>0.5223±0.0053</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.5382±0.0000</t>
+          <t>0.5309±0.0060</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.5472±0.0000</t>
+          <t>0.5244±0.0074</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.4855±0.0000</t>
+          <t>0.4855±0.0002</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5166±0.0027</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.5143±0.0000</t>
+          <t>0.5145±0.0001</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5322±0.0000</t>
+          <t>0.5240±0.0041</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5176±0.0024</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5210±0.0088</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5206±0.0000</t>
+          <t>0.5151±0.0011</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5144±0.0009</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5144±0.0009</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5144±0.0009</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.5155±0.0000</t>
+          <t>0.5168±0.0049</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5225±0.0087</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5284±0.0000</t>
+          <t>0.5179±0.0052</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.4855±0.0000</t>
+          <t>0.4855±0.0002</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5186±0.0067</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5206±0.0085</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5211±0.0091</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5152±0.0000</t>
+          <t>0.5241±0.0146</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5150±0.0006</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5188±0.0055</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5154±0.0013</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5154±0.0013</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5154±0.0013</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5173±0.0022</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5155±0.0022</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5149±0.0000</t>
+          <t>0.5216±0.0049</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.4855±0.0000</t>
+          <t>0.4855±0.0002</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5184±0.0000</t>
+          <t>0.5163±0.0014</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5143±0.0000</t>
+          <t>0.5262±0.0170</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5336±0.0000</t>
+          <t>0.5141±0.0058</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5337±0.0000</t>
+          <t>0.5304±0.0095</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5195±0.0040</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5165±0.0000</t>
+          <t>0.5185±0.0055</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5258±0.0000</t>
+          <t>0.5198±0.0042</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5258±0.0000</t>
+          <t>0.5198±0.0042</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5258±0.0000</t>
+          <t>0.5198±0.0042</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5321±0.0000</t>
+          <t>0.5129±0.0016</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5194±0.0000</t>
+          <t>0.5239±0.0134</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5222±0.0000</t>
+          <t>0.5178±0.0044</t>
         </is>
       </c>
     </row>
@@ -1360,62 +1360,62 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6793±0.0004</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6794±0.0001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6733±0.0066</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6789±0.0003</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6768±0.0025</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.6789±0.0000</t>
+          <t>0.6791±0.0002</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6795±0.0005</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6795±0.0005</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6795±0.0005</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.6793±0.0000</t>
+          <t>0.6792±0.0004</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6638±0.0000</t>
+          <t>0.6490±0.0216</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6784±0.0006</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1425,192 +1425,192 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.6778±0.0000</t>
+          <t>0.6789±0.0001</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.6767±0.0000</t>
+          <t>0.6756±0.0021</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6755±0.0018</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.6790±0.0000</t>
+          <t>0.6779±0.0015</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.6788±0.0000</t>
+          <t>0.6801±0.0006</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.6779±0.0000</t>
+          <t>0.6792±0.0003</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.6777±0.0000</t>
+          <t>0.6785±0.0007</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.6777±0.0000</t>
+          <t>0.6785±0.0007</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.6777±0.0000</t>
+          <t>0.6785±0.0007</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.6799±0.0000</t>
+          <t>0.6790±0.0004</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6794±0.0001</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.6793±0.0000</t>
+          <t>0.6793±0.0004</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.0025±0.0000</t>
+          <t>0.0031±0.0029</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.6789±0.0000</t>
+          <t>0.6760±0.0046</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.6791±0.0000</t>
+          <t>0.6726±0.0040</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.6790±0.0000</t>
+          <t>0.6741±0.0045</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.6779±0.0000</t>
+          <t>0.6738±0.0054</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.6769±0.0000</t>
+          <t>0.6790±0.0008</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.6783±0.0000</t>
+          <t>0.6783±0.0006</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.6759±0.0000</t>
+          <t>0.6786±0.0012</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.6759±0.0000</t>
+          <t>0.6786±0.0012</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.6759±0.0000</t>
+          <t>0.6786±0.0012</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.6792±0.0000</t>
+          <t>0.6785±0.0010</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.6657±0.0000</t>
+          <t>0.6566±0.0057</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.6745±0.0000</t>
+          <t>0.6732±0.0053</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.0010±0.0000</t>
+          <t>0.0039±0.0010</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.6739±0.0000</t>
+          <t>0.6727±0.0041</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6765±0.0013</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.6712±0.0000</t>
+          <t>0.6691±0.0054</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.6780±0.0000</t>
+          <t>0.6787±0.0041</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.6777±0.0000</t>
+          <t>0.6792±0.0004</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.6708±0.0000</t>
+          <t>0.6749±0.0010</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.6720±0.0000</t>
+          <t>0.6694±0.0054</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.6720±0.0000</t>
+          <t>0.6694±0.0054</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.6720±0.0000</t>
+          <t>0.6694±0.0054</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.6770±0.0000</t>
+          <t>0.6727±0.0035</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.6740±0.0000</t>
+          <t>0.6562±0.0132</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.6676±0.0000</t>
+          <t>0.6699±0.0090</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1620,62 +1620,62 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6790±0.0001</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.6792±0.0000</t>
+          <t>0.6794±0.0001</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.6777±0.0000</t>
+          <t>0.6718±0.0057</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6795±0.0009</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6771±0.0029</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.6753±0.0000</t>
+          <t>0.6788±0.0002</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6791±0.0007</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6791±0.0007</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6791±0.0007</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.6729±0.0000</t>
+          <t>0.6777±0.0008</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6691±0.0060</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.6564±0.0000</t>
+          <t>0.6787±0.0002</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1685,62 +1685,62 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6758±0.0025</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6787±0.0011</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6765±0.0033</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.6797±0.0000</t>
+          <t>0.6774±0.0011</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6789±0.0008</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6795±0.0009</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6790±0.0005</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6790±0.0005</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6790±0.0005</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.6782±0.0013</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6709±0.0027</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.6796±0.0000</t>
+          <t>0.6759±0.0016</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -1750,62 +1750,62 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6723±0.0000</t>
+          <t>0.6751±0.0011</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6785±0.0000</t>
+          <t>0.6782±0.0013</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6763±0.0000</t>
+          <t>0.6652±0.0131</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6726±0.0000</t>
+          <t>0.6752±0.0031</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6784±0.0000</t>
+          <t>0.6774±0.0007</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6726±0.0000</t>
+          <t>0.6709±0.0051</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6646±0.0000</t>
+          <t>0.6765±0.0012</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6646±0.0000</t>
+          <t>0.6765±0.0012</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6646±0.0000</t>
+          <t>0.6765±0.0012</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6698±0.0000</t>
+          <t>0.6756±0.0007</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6749±0.0000</t>
+          <t>0.6771±0.0031</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6668±0.0000</t>
+          <t>0.6742±0.0010</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.6233±0.0070</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.4533±0.0000</t>
+          <t>0.5468±0.0564</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.4995±0.0000</t>
+          <t>0.4999±0.0001</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.4998±0.0000</t>
+          <t>0.5427±0.0336</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.5513±0.0411</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.5559±0.0293</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.5879±0.0396</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.6325±0.0059</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.6325±0.0059</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.6325±0.0059</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.5584±0.0441</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.5567±0.0037</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.5797±0.0073</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.4196±0.0050</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.5604±0.0214</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.5133±0.0029</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.6045±0.0177</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.5592±0.0140</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.5774±0.0552</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.5622±0.0114</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.6321±0.0154</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.6321±0.0154</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.6321±0.0154</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.5576±0.0116</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.6017±0.0005</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.5879±0.0312</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.4207±0.0482</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.5051±0.0064</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.5509±0.0137</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.5495±0.0188</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.5539±0.0109</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.5445±0.0248</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.5446±0.0254</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.5771±0.0045</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.5771±0.0045</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.5771±0.0045</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.5303±0.0058</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.5863±0.0034</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.5652±0.0066</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.5203±0.0193</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.5646±0.0109</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.5001±0.0014</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.5435±0.0123</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.5809±0.0071</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.5514±0.0074</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.5553±0.0188</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.5224±0.0014</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.5224±0.0014</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.5224±0.0014</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.5354±0.0076</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.5442±0.0048</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.5518±0.0249</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.6354±0.0095</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.6047±0.0018</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.4824±0.0000</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.5003±0.0000</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.5003±0.0000</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.5003±0.0000</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.4763±0.0000</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.5546±0.0000</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.5005±0.0000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.4059±0.0000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.4760±0.0000</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0.5277±0.0000</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0.5003±0.0000</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.5356±0.0000</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.5740±0.0000</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0.5149±0.0000</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.5259±0.0000</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.5259±0.0000</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.5259±0.0000</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.5404±0.0000</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.6038±0.0000</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.5357±0.0000</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.4934±0.0000</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.4803±0.0000</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>0.4998±0.0000</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.5131±0.0000</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0.5031±0.0000</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.4736±0.0000</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.5096±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0.5096±0.0000</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0.5096±0.0000</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>0.4963±0.0000</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0.5807±0.0000</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>0.5080±0.0000</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>0.5230±0.0000</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0.5277±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.5003±0.0000</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.5097±0.0000</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>0.5276±0.0000</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>0.5340±0.0000</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>0.5406±0.0000</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>0.5421±0.0000</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>0.5421±0.0000</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>0.5421±0.0000</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>0.5494±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.5904±0.0000</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>0.5387±0.0000</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>0.6112±0.0000</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>0.4751±0.0000</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0.4991±0.0000</t>
-        </is>
-      </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0.5940±0.0104</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.5946±0.0142</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.5950±0.0295</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.5714±0.0326</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.6196±0.0466</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.6196±0.0466</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.6196±0.0466</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.4984±0.0313</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.5552±0.0019</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>0.5824±0.0191</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>0.6332±0.0095</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>0.6006±0.0199</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0.5110±0.0157</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0.5691±0.0504</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0.5909±0.0048</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0.5808±0.0616</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0.5516±0.0272</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0.5899±0.0637</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>0.5899±0.0637</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>0.5899±0.0637</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>0.5424±0.0229</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>0.5628±0.0028</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>0.5739±0.0256</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>0.4979±0.0000</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>0.4821±0.0000</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>0.4999±0.0000</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.4946±0.0000</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.5653±0.0000</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>0.5128±0.0000</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>0.6063±0.0000</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>0.4543±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>0.5001±0.0000</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0.5002±0.0000</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>0.5005±0.0000</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0.4538±0.0000</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>0.5005±0.0000</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>0.5005±0.0000</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>0.5005±0.0000</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0.4525±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>0.5647±0.0000</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>0.5005±0.0000</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>0.5005±0.0000</t>
-        </is>
-      </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.5529±0.0000</t>
+          <t>0.5929±0.0353</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4999±0.0000</t>
+          <t>0.5132±0.0194</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.5170±0.0000</t>
+          <t>0.5433±0.0243</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.5273±0.0000</t>
+          <t>0.5922±0.0183</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.6007±0.0000</t>
+          <t>0.6132±0.0179</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.5402±0.0000</t>
+          <t>0.6019±0.0114</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.5502±0.0000</t>
+          <t>0.6138±0.0073</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.5502±0.0000</t>
+          <t>0.6138±0.0073</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.5502±0.0000</t>
+          <t>0.6138±0.0073</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.5547±0.0000</t>
+          <t>0.5968±0.0095</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.5727±0.0000</t>
+          <t>0.5803±0.0023</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.5754±0.0000</t>
+          <t>0.5910±0.0080</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6083±0.0000</t>
+          <t>0.6308±0.0106</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.4820±0.0000</t>
+          <t>0.5464±0.0414</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5142±0.0000</t>
+          <t>0.5145±0.0002</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5525±0.0427</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5424±0.0253</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5396±0.0200</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.4957±0.0000</t>
+          <t>0.5593±0.0318</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.6246±0.0149</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.6246±0.0149</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.6246±0.0149</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.4923±0.0000</t>
+          <t>0.5422±0.0313</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.5527±0.0000</t>
+          <t>0.5553±0.0043</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5562±0.0043</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.4500±0.0000</t>
+          <t>0.4495±0.0084</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.4929±0.0000</t>
+          <t>0.5439±0.0141</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5290±0.0000</t>
+          <t>0.5214±0.0017</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.6140±0.0307</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.5389±0.0000</t>
+          <t>0.5469±0.0147</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.5581±0.0000</t>
+          <t>0.5613±0.0330</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.5154±0.0000</t>
+          <t>0.5556±0.0044</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.5428±0.0000</t>
+          <t>0.6008±0.0226</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5428±0.0000</t>
+          <t>0.6008±0.0226</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.5428±0.0000</t>
+          <t>0.6008±0.0226</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.5308±0.0000</t>
+          <t>0.5499±0.0173</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.5856±0.0000</t>
+          <t>0.5815±0.0029</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.5413±0.0000</t>
+          <t>0.5672±0.0184</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.5129±0.0000</t>
+          <t>0.4594±0.0366</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.4998±0.0000</t>
+          <t>0.5125±0.0013</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5497±0.0124</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5493±0.0171</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.5212±0.0000</t>
+          <t>0.5449±0.0055</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.5160±0.0000</t>
+          <t>0.5497±0.0219</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.5054±0.0000</t>
+          <t>0.5381±0.0156</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.5194±0.0000</t>
+          <t>0.5699±0.0081</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.5194±0.0000</t>
+          <t>0.5699±0.0081</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.5194±0.0000</t>
+          <t>0.5699±0.0081</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.5126±0.0000</t>
+          <t>0.5303±0.0040</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.5702±0.0000</t>
+          <t>0.5766±0.0025</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.5185±0.0000</t>
+          <t>0.5570±0.0039</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.5189±0.0000</t>
+          <t>0.5064±0.0145</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.5198±0.0000</t>
+          <t>0.5542±0.0112</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5146±0.0007</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5196±0.0000</t>
+          <t>0.5498±0.0157</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.5288±0.0000</t>
+          <t>0.5606±0.0048</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.5328±0.0000</t>
+          <t>0.5380±0.0046</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.5253±0.0000</t>
+          <t>0.5424±0.0172</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.5371±0.0000</t>
+          <t>0.5211±0.0050</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.5371±0.0000</t>
+          <t>0.5211±0.0050</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.5371±0.0000</t>
+          <t>0.5211±0.0050</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.5420±0.0000</t>
+          <t>0.5272±0.0081</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.5770±0.0000</t>
+          <t>0.5386±0.0030</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.5353±0.0000</t>
+          <t>0.5487±0.0230</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6193±0.0000</t>
+          <t>0.6436±0.0107</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.4898±0.0000</t>
+          <t>0.5864±0.0037</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5140±0.0000</t>
+          <t>0.5145±0.0002</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.5082±0.0000</t>
+          <t>0.5951±0.0207</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.5134±0.0000</t>
+          <t>0.5801±0.0147</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5716±0.0224</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.4972±0.0000</t>
+          <t>0.5569±0.0322</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.6168±0.0613</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.6168±0.0613</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.6168±0.0613</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.5010±0.0000</t>
+          <t>0.5035±0.0187</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.5608±0.0000</t>
+          <t>0.5516±0.0018</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.5119±0.0000</t>
+          <t>0.5606±0.0192</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.6144±0.0000</t>
+          <t>0.6413±0.0108</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.4787±0.0000</t>
+          <t>0.5768±0.0195</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5187±0.0059</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.5145±0.0000</t>
+          <t>0.5796±0.0500</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.5146±0.0000</t>
+          <t>0.5827±0.0152</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5660±0.0431</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.4797±0.0000</t>
+          <t>0.5370±0.0190</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5912±0.0544</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5912±0.0544</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5912±0.0544</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.4776±0.0000</t>
+          <t>0.5333±0.0175</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.5603±0.0000</t>
+          <t>0.5588±0.0026</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5618±0.0285</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.5152±0.0000</t>
+          <t>0.5145±0.0002</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.5595±0.0000</t>
+          <t>0.5821±0.0338</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5144±0.0000</t>
+          <t>0.5207±0.0091</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5222±0.0000</t>
+          <t>0.5496±0.0276</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.5291±0.0000</t>
+          <t>0.5765±0.0170</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.5795±0.0000</t>
+          <t>0.5877±0.0208</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.5481±0.0000</t>
+          <t>0.5863±0.0087</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.5499±0.0000</t>
+          <t>0.5927±0.0135</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.5499±0.0000</t>
+          <t>0.5927±0.0135</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.5499±0.0000</t>
+          <t>0.5926±0.0135</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.5564±0.0000</t>
+          <t>0.5751±0.0103</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.5664±0.0000</t>
+          <t>0.5693±0.0015</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.5656±0.0000</t>
+          <t>0.5693±0.0094</t>
         </is>
       </c>
     </row>
